--- a/Hand_edited_log/1/student/dungdvhe181404/TC6/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungdvhe181404/TC6/GradeDetail.xlsx
@@ -1092,10 +1092,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>62935</x:v>
+        <x:v>51782</x:v>
       </x:c>
       <x:c r="Q2" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>48</x:v>
@@ -1148,10 +1148,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P3" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>62935</x:v>
+        <x:v>51782</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>48</x:v>
@@ -1204,10 +1204,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>62935</x:v>
+        <x:v>51782</x:v>
       </x:c>
       <x:c r="Q4" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="R4" s="2" t="s">
         <x:v>48</x:v>
@@ -1260,10 +1260,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>62935</x:v>
+        <x:v>51782</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="R5" s="2" t="s">
         <x:v>48</x:v>
@@ -1316,10 +1316,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>62935</x:v>
+        <x:v>51782</x:v>
       </x:c>
       <x:c r="R6" s="2" t="s">
         <x:v>48</x:v>
@@ -1372,10 +1372,10 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="P7" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="Q7" s="0">
-        <x:v>62935</x:v>
+        <x:v>51782</x:v>
       </x:c>
       <x:c r="R7" s="2" t="s">
         <x:v>48</x:v>
@@ -1428,10 +1428,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>62935</x:v>
+        <x:v>51782</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="R8" s="2" t="s">
         <x:v>48</x:v>
@@ -1484,10 +1484,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>62935</x:v>
+        <x:v>51782</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>63</x:v>
@@ -1540,10 +1540,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>62935</x:v>
+        <x:v>51782</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="R10" s="3" t="s">
         <x:v>63</x:v>
@@ -1596,10 +1596,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>62935</x:v>
+        <x:v>51782</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="R11" s="3" t="s">
         <x:v>63</x:v>
@@ -1652,10 +1652,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P12" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="Q12" s="0">
-        <x:v>62935</x:v>
+        <x:v>51782</x:v>
       </x:c>
       <x:c r="R12" s="3" t="s">
         <x:v>63</x:v>
@@ -1708,10 +1708,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P13" s="0">
-        <x:v>62943</x:v>
+        <x:v>63481</x:v>
       </x:c>
       <x:c r="Q13" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="R13" s="2" t="s">
         <x:v>48</x:v>
@@ -1764,10 +1764,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P14" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="Q14" s="0">
-        <x:v>62943</x:v>
+        <x:v>63481</x:v>
       </x:c>
       <x:c r="R14" s="2" t="s">
         <x:v>48</x:v>
@@ -1820,10 +1820,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P15" s="0">
-        <x:v>62943</x:v>
+        <x:v>63481</x:v>
       </x:c>
       <x:c r="Q15" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="R15" s="2" t="s">
         <x:v>48</x:v>
@@ -1876,10 +1876,10 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="P16" s="0">
-        <x:v>62943</x:v>
+        <x:v>63481</x:v>
       </x:c>
       <x:c r="Q16" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="R16" s="2" t="s">
         <x:v>48</x:v>
@@ -1932,10 +1932,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P17" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="Q17" s="0">
-        <x:v>62943</x:v>
+        <x:v>63481</x:v>
       </x:c>
       <x:c r="R17" s="2" t="s">
         <x:v>48</x:v>
@@ -1988,10 +1988,10 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="P18" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="Q18" s="0">
-        <x:v>62943</x:v>
+        <x:v>63481</x:v>
       </x:c>
       <x:c r="R18" s="2" t="s">
         <x:v>48</x:v>
@@ -2044,10 +2044,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P19" s="0">
-        <x:v>62943</x:v>
+        <x:v>63481</x:v>
       </x:c>
       <x:c r="Q19" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="R19" s="2" t="s">
         <x:v>48</x:v>
@@ -2100,10 +2100,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P20" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="Q20" s="0">
-        <x:v>62943</x:v>
+        <x:v>63481</x:v>
       </x:c>
       <x:c r="R20" s="3" t="s">
         <x:v>63</x:v>
@@ -2156,10 +2156,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P21" s="0">
-        <x:v>62943</x:v>
+        <x:v>63481</x:v>
       </x:c>
       <x:c r="Q21" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="R21" s="3" t="s">
         <x:v>63</x:v>
@@ -2212,10 +2212,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P22" s="0">
-        <x:v>62943</x:v>
+        <x:v>63481</x:v>
       </x:c>
       <x:c r="Q22" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="R22" s="3" t="s">
         <x:v>63</x:v>
@@ -2268,10 +2268,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P23" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="Q23" s="0">
-        <x:v>62943</x:v>
+        <x:v>63481</x:v>
       </x:c>
       <x:c r="R23" s="3" t="s">
         <x:v>63</x:v>
